--- a/marketing_report/outputs/Grado_Pregrado/Analisis_UTM/analisis_utm_completo.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/Analisis_UTM/analisis_utm_completo.xlsx
@@ -472,19 +472,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>49137</v>
+        <v>49138</v>
       </c>
       <c r="C2" t="n">
-        <v>24133</v>
+        <v>24134</v>
       </c>
       <c r="D2" t="n">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="E2" t="n">
-        <v>56784</v>
+        <v>56777</v>
       </c>
       <c r="F2" t="n">
-        <v>5.77</v>
+        <v>5.76</v>
       </c>
     </row>
     <row r="3">
@@ -544,13 +544,13 @@
         <v>1785</v>
       </c>
       <c r="D5" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E5" t="n">
         <v>2166</v>
       </c>
       <c r="F5" t="n">
-        <v>8.460000000000001</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="6">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11746</v>
+        <v>11747</v>
       </c>
       <c r="C2" t="n">
         <v>5130</v>
@@ -936,19 +936,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6515</v>
+        <v>6516</v>
       </c>
       <c r="C3" t="n">
-        <v>6666</v>
+        <v>6667</v>
       </c>
       <c r="D3" t="n">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E3" t="n">
-        <v>8244</v>
+        <v>8237</v>
       </c>
       <c r="F3" t="n">
-        <v>11.21</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="4">
@@ -1002,7 +1002,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4227</v>
+        <v>4226</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>4015</v>
       </c>
       <c r="D7" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E7" t="n">
         <v>4645</v>
       </c>
       <c r="F7" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="8">
@@ -3292,16 +3292,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48832</v>
+        <v>48833</v>
       </c>
       <c r="C2" t="n">
-        <v>23790</v>
+        <v>23791</v>
       </c>
       <c r="D2" t="n">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="E2" t="n">
-        <v>56433</v>
+        <v>56426</v>
       </c>
       <c r="F2" t="n">
         <v>5.75</v>
@@ -3342,13 +3342,13 @@
         <v>4015</v>
       </c>
       <c r="D4" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E4" t="n">
         <v>4645</v>
       </c>
       <c r="F4" t="n">
-        <v>4.38</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="5">
@@ -3712,7 +3712,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2983</v>
+        <v>2982</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -3800,7 +3800,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="C6" t="n">
         <v>1877</v>
@@ -26968,7 +26968,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4469</v>
+        <v>4470</v>
       </c>
       <c r="C2" t="n">
         <v>2416</v>
@@ -27012,7 +27012,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2728</v>
+        <v>2727</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -27062,13 +27062,13 @@
         <v>2489</v>
       </c>
       <c r="D6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E6" t="n">
         <v>2774</v>
       </c>
       <c r="F6" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="7">
@@ -63945,7 +63945,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="n">
-        <v>60037</v>
+        <v>60038</v>
       </c>
       <c r="D2" t="n">
         <v>1669</v>
@@ -63961,7 +63961,7 @@
         <v>106</v>
       </c>
       <c r="C3" t="n">
-        <v>59486</v>
+        <v>59487</v>
       </c>
       <c r="D3" t="n">
         <v>1638</v>
@@ -63977,7 +63977,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="n">
-        <v>59670</v>
+        <v>59671</v>
       </c>
       <c r="D4" t="n">
         <v>1636</v>
@@ -64012,7 +64012,7 @@
         <v>46423</v>
       </c>
       <c r="D6" t="n">
-        <v>530</v>
+        <v>531</v>
       </c>
     </row>
   </sheetData>
